--- a/output/upload/S00027_1809_연금저축_미래로기업복지연금보험.xlsx
+++ b/output/upload/S00027_1809_연금저축_미래로기업복지연금보험.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW27"/>
+  <dimension ref="A1:AW102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
@@ -3061,11 +3061,11 @@
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N12" s="6" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>X55</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
@@ -3144,11 +3144,11 @@
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>X56</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
@@ -3227,11 +3227,11 @@
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N14" s="6" t="n">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>N7</t>
+          <t>X57</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -3306,11 +3306,11 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>X58</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -3351,11 +3351,11 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>X59</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -3396,11 +3396,11 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -3441,11 +3441,11 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X61</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -3486,11 +3486,11 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>999</v>
+        <v>61</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>X62</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3531,11 +3531,11 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>X63</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3576,11 +3576,11 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>N7</t>
+          <t>X64</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>X65</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3666,11 +3666,11 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>X66</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3711,11 +3711,11 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X67</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3756,11 +3756,11 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>A999</t>
+          <t>X68</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3801,11 +3801,11 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>999</v>
+        <v>68</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -3833,26 +3833,3401 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t>X69</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>999</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>69</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>X70</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>999</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>70</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>X71</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>999</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>71</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>X72</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>999</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>72</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>X73</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>999</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>73</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>X74</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>999</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>74</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>X75</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>999</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>75</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>X76</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>999</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>76</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>X77</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>999</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>77</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>X78</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>999</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>78</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>X79</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>999</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>79</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>X80</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>999</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>80</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>999</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>5</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>N7</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>999</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>7</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>999</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>10</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>N15</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>999</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>15</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>999</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>20</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
           <t>N0</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>999</v>
-      </c>
-      <c r="M27" t="inlineStr">
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>999</v>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="N27" t="n">
+      <c r="N44" t="n">
         <v>0</v>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>X55</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>999</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>55</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>X56</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>999</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>56</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>X57</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>999</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>57</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>X58</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>999</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>58</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>X59</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>999</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>59</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>X60</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>999</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>60</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>X61</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>999</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>61</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>X62</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>999</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>62</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>X63</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>999</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>63</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>X64</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>999</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>64</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>X65</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>999</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>65</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>X66</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>999</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>66</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>X67</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>999</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>67</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>X68</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>999</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>68</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>X69</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>999</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>69</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>X70</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>999</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>70</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>X71</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>999</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>71</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>X72</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>999</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>72</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>X73</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>999</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>73</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>X74</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>999</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>74</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>X75</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>999</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>75</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>X76</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>999</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>76</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>X77</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>999</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>77</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>X78</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>999</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>78</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>X79</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>999</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>79</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>X80</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>999</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>80</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>999</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>5</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>N7</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>999</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>7</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>999</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>10</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>N15</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>999</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>15</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>999</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>20</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>999</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>X55</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>999</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>55</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>X56</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>999</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>56</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>X57</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>999</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>57</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>X58</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>999</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>58</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>X59</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>999</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>59</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>X60</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>999</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>60</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>X61</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>999</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>61</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>X62</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>999</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>62</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>X63</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>999</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>63</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>X64</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>999</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>64</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>X65</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>999</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>65</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>X66</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>999</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>66</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>X67</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>999</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>67</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>X68</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>999</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>68</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>X69</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
+        <v>999</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>69</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>X70</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>999</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>70</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>X71</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>999</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>71</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>X72</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>999</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>72</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>X73</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>999</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>73</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>X74</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>999</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>74</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>X75</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>999</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>75</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>X76</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>999</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>76</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>X77</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
+        <v>999</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>77</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>X78</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L100" t="n">
+        <v>999</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>78</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>X79</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L101" t="n">
+        <v>999</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>79</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>X80</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L102" t="n">
+        <v>999</v>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>80</v>
+      </c>
+      <c r="O102" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
         </is>

--- a/output/upload/S00027_1809_연금저축_미래로기업복지연금보험.xlsx
+++ b/output/upload/S00027_1809_연금저축_미래로기업복지연금보험.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW111"/>
+  <dimension ref="A1:AW146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -5078,7 +5078,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8206,7 +8206,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8342,7 +8342,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8818,7 +8818,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -9158,7 +9158,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -9430,7 +9430,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -9770,7 +9770,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -9838,7 +9838,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>180973</t>
+          <t>1809073</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -10024,6 +10024,2386 @@
         <v>80</v>
       </c>
       <c r="O111" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L112" t="n">
+        <v>999</v>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>5</v>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>N6</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L113" t="n">
+        <v>999</v>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>6</v>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>N7</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L114" t="n">
+        <v>999</v>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>7</v>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>N8</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L115" t="n">
+        <v>999</v>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>8</v>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>N9</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L116" t="n">
+        <v>999</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>9</v>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L117" t="n">
+        <v>999</v>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>10</v>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>N15</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
+        <v>999</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>15</v>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L119" t="n">
+        <v>999</v>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>20</v>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L120" t="n">
+        <v>999</v>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>X55</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L121" t="n">
+        <v>999</v>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>55</v>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>X56</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L122" t="n">
+        <v>999</v>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>56</v>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>X57</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>999</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>57</v>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>X58</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L124" t="n">
+        <v>999</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>58</v>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>X59</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L125" t="n">
+        <v>999</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>59</v>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>X60</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
+        <v>999</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>60</v>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>X61</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>999</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>61</v>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>X62</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
+        <v>999</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>62</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>X63</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>999</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>63</v>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>X64</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>999</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>64</v>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>X65</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
+        <v>999</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>65</v>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>X66</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>999</v>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>66</v>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>X67</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
+        <v>999</v>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>67</v>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>X68</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>999</v>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>68</v>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>X69</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L135" t="n">
+        <v>999</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>69</v>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>X70</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
+        <v>999</v>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>70</v>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>X71</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L137" t="n">
+        <v>999</v>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>71</v>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>X72</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
+        <v>999</v>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>72</v>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>X73</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L139" t="n">
+        <v>999</v>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>73</v>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>X74</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L140" t="n">
+        <v>999</v>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>74</v>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>X75</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L141" t="n">
+        <v>999</v>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>75</v>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>X76</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L142" t="n">
+        <v>999</v>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>76</v>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>X77</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L143" t="n">
+        <v>999</v>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>77</v>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>X78</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L144" t="n">
+        <v>999</v>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>78</v>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>X79</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L145" t="n">
+        <v>999</v>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>79</v>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>1809073</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>한화생명 연금저축 미래로기업복지연금보험(2종 계좌이체용)적립형 종신연금형</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>X80</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L146" t="n">
+        <v>999</v>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
+        <v>80</v>
+      </c>
+      <c r="O146" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
         </is>
